--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/191.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/191.xlsx
@@ -426,13 +426,13 @@
         <v>-11.1686214309318</v>
       </c>
       <c r="E2">
-        <v>-15.92136948946531</v>
+        <v>-16.79006212988271</v>
       </c>
       <c r="F2">
-        <v>3.855668396669691</v>
+        <v>1.189469397614988</v>
       </c>
       <c r="G2">
-        <v>-7.850582494858477</v>
+        <v>-10.23262594782135</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-11.01708798777442</v>
       </c>
       <c r="E3">
-        <v>-15.94212801431647</v>
+        <v>-15.97173517737862</v>
       </c>
       <c r="F3">
-        <v>3.732201099796116</v>
+        <v>1.089654748588501</v>
       </c>
       <c r="G3">
-        <v>-7.812411904790681</v>
+        <v>-6.845921308419232</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-10.81033983180548</v>
       </c>
       <c r="E4">
-        <v>-16.93453403614942</v>
+        <v>-17.44512853746227</v>
       </c>
       <c r="F4">
-        <v>3.813972587328001</v>
+        <v>1.557460887832413</v>
       </c>
       <c r="G4">
-        <v>-7.121060748188061</v>
+        <v>-8.486753478412524</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-10.55436615199775</v>
       </c>
       <c r="E5">
-        <v>-16.98980858988704</v>
+        <v>-18.34826927965601</v>
       </c>
       <c r="F5">
-        <v>4.206730070651068</v>
+        <v>1.539287862452746</v>
       </c>
       <c r="G5">
-        <v>-7.512552621480114</v>
+        <v>-8.082516004794277</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-10.23891566655088</v>
       </c>
       <c r="E6">
-        <v>-18.5934499193793</v>
+        <v>-18.96836228247433</v>
       </c>
       <c r="F6">
-        <v>4.226984085603624</v>
+        <v>1.628456840315648</v>
       </c>
       <c r="G6">
-        <v>-7.376075381623659</v>
+        <v>-9.053873103108455</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-9.865587992864645</v>
       </c>
       <c r="E7">
-        <v>-18.13822054128423</v>
+        <v>-17.65508217787989</v>
       </c>
       <c r="F7">
-        <v>4.235705554079948</v>
+        <v>1.423720090685383</v>
       </c>
       <c r="G7">
-        <v>-7.317084770659386</v>
+        <v>-7.378495390412867</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-9.435678685812503</v>
       </c>
       <c r="E8">
-        <v>-18.92261563804884</v>
+        <v>-21.06260490053557</v>
       </c>
       <c r="F8">
-        <v>4.119349096766697</v>
+        <v>2.342130155519704</v>
       </c>
       <c r="G8">
-        <v>-6.868393291539805</v>
+        <v>-8.216834768959128</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-8.960474976416661</v>
       </c>
       <c r="E9">
-        <v>-20.2272871135547</v>
+        <v>-20.00797764583724</v>
       </c>
       <c r="F9">
-        <v>3.967813779953789</v>
+        <v>1.792663388157987</v>
       </c>
       <c r="G9">
-        <v>-6.736362114342591</v>
+        <v>-7.481526188686065</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-8.456826139129777</v>
       </c>
       <c r="E10">
-        <v>-19.42807032136298</v>
+        <v>-21.8495495281665</v>
       </c>
       <c r="F10">
-        <v>4.551003981078873</v>
+        <v>1.910765089390053</v>
       </c>
       <c r="G10">
-        <v>-5.208707564700363</v>
+        <v>-5.505872063941963</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-7.941275562154844</v>
       </c>
       <c r="E11">
-        <v>-20.398671740849</v>
+        <v>-20.79325126655934</v>
       </c>
       <c r="F11">
-        <v>4.852091814898559</v>
+        <v>2.58907266779643</v>
       </c>
       <c r="G11">
-        <v>-4.17387737676174</v>
+        <v>-4.833596270736623</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-7.437719657698986</v>
       </c>
       <c r="E12">
-        <v>-19.90570658884801</v>
+        <v>-22.85350768719301</v>
       </c>
       <c r="F12">
-        <v>4.954096729206098</v>
+        <v>2.600769919687866</v>
       </c>
       <c r="G12">
-        <v>-4.21298816176269</v>
+        <v>-6.158493148280649</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.966473765695426</v>
       </c>
       <c r="E13">
-        <v>-22.95776674427161</v>
+        <v>-22.70226571228484</v>
       </c>
       <c r="F13">
-        <v>4.622847216226868</v>
+        <v>2.463380264111663</v>
       </c>
       <c r="G13">
-        <v>-3.968762596239575</v>
+        <v>-5.70656395562366</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.558991844972016</v>
       </c>
       <c r="E14">
-        <v>-23.36352707230689</v>
+        <v>-24.216111930679</v>
       </c>
       <c r="F14">
-        <v>5.167057663655241</v>
+        <v>3.188209203784074</v>
       </c>
       <c r="G14">
-        <v>-4.201841554931963</v>
+        <v>-4.438939515909026</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.228802604184819</v>
       </c>
       <c r="E15">
-        <v>-23.43562943545701</v>
+        <v>-25.82725241312796</v>
       </c>
       <c r="F15">
-        <v>5.544236231888131</v>
+        <v>2.553056027867506</v>
       </c>
       <c r="G15">
-        <v>-3.479540108082697</v>
+        <v>-3.470965795135985</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.989761640514704</v>
       </c>
       <c r="E16">
-        <v>-26.10590753271595</v>
+        <v>-25.89334549126991</v>
       </c>
       <c r="F16">
-        <v>6.158671367018919</v>
+        <v>3.639231227736159</v>
       </c>
       <c r="G16">
-        <v>-3.225422632488241</v>
+        <v>-4.757930441891041</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.843088489356346</v>
       </c>
       <c r="E17">
-        <v>-24.69157000216633</v>
+        <v>-27.4400367316417</v>
       </c>
       <c r="F17">
-        <v>5.704047995815125</v>
+        <v>3.648039800037833</v>
       </c>
       <c r="G17">
-        <v>-2.374744850717116</v>
+        <v>-3.3477969483474</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.79012721499794</v>
       </c>
       <c r="E18">
-        <v>-25.37354460229946</v>
+        <v>-26.93104078165356</v>
       </c>
       <c r="F18">
-        <v>6.090659116480373</v>
+        <v>3.84919579059329</v>
       </c>
       <c r="G18">
-        <v>-2.080526737005469</v>
+        <v>-3.065205470569673</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.821040977820871</v>
       </c>
       <c r="E19">
-        <v>-27.68886279294117</v>
+        <v>-27.56764460070385</v>
       </c>
       <c r="F19">
-        <v>6.170699613446682</v>
+        <v>3.137098262775097</v>
       </c>
       <c r="G19">
-        <v>-2.063834966396463</v>
+        <v>-4.887783280123414</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.922062404403289</v>
       </c>
       <c r="E20">
-        <v>-28.24797536477219</v>
+        <v>-29.80194612711132</v>
       </c>
       <c r="F20">
-        <v>6.236380648877702</v>
+        <v>4.52913458609257</v>
       </c>
       <c r="G20">
-        <v>-1.157655888659457</v>
+        <v>-3.629689901016342</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-6.078415261781419</v>
       </c>
       <c r="E21">
-        <v>-29.4344174408858</v>
+        <v>-28.7603721987401</v>
       </c>
       <c r="F21">
-        <v>6.378052645249253</v>
+        <v>4.519915833958796</v>
       </c>
       <c r="G21">
-        <v>-1.168905122401901</v>
+        <v>-1.602103248397693</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-6.27408856436386</v>
       </c>
       <c r="E22">
-        <v>-28.65709582052116</v>
+        <v>-30.4962879897594</v>
       </c>
       <c r="F22">
-        <v>6.142025034141735</v>
+        <v>3.829313946530863</v>
       </c>
       <c r="G22">
-        <v>-1.25185415143388</v>
+        <v>-3.075229802462586</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.497456311726676</v>
       </c>
       <c r="E23">
-        <v>-29.18837186262704</v>
+        <v>-28.03224791999479</v>
       </c>
       <c r="F23">
-        <v>6.538025947179623</v>
+        <v>4.379198812254256</v>
       </c>
       <c r="G23">
-        <v>-1.387894399279151</v>
+        <v>-2.50959330216825</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-6.730774606630709</v>
       </c>
       <c r="E24">
-        <v>-30.04406325416842</v>
+        <v>-30.72024367180874</v>
       </c>
       <c r="F24">
-        <v>6.743456360000851</v>
+        <v>3.8512688616366</v>
       </c>
       <c r="G24">
-        <v>-0.410618045540757</v>
+        <v>-0.7972301747079248</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-6.966629276964984</v>
       </c>
       <c r="E25">
-        <v>-30.54440981880191</v>
+        <v>-32.18818701342415</v>
       </c>
       <c r="F25">
-        <v>6.899489401613606</v>
+        <v>4.938079127577343</v>
       </c>
       <c r="G25">
-        <v>-0.6259491695971121</v>
+        <v>-4.080735178014344</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-7.196750664579138</v>
       </c>
       <c r="E26">
-        <v>-31.15996076219053</v>
+        <v>-32.71626368864361</v>
       </c>
       <c r="F26">
-        <v>6.971533767412863</v>
+        <v>4.398819344840635</v>
       </c>
       <c r="G26">
-        <v>-0.317204382059142</v>
+        <v>-1.51394673123244</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.421615387314738</v>
       </c>
       <c r="E27">
-        <v>-31.43999706635086</v>
+        <v>-31.54700717138912</v>
       </c>
       <c r="F27">
-        <v>6.772545870255643</v>
+        <v>4.223148349876429</v>
       </c>
       <c r="G27">
-        <v>0.5248461180366415</v>
+        <v>-1.524636482778747</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.635052540059237</v>
       </c>
       <c r="E28">
-        <v>-31.2105936300703</v>
+        <v>-31.69273346495595</v>
       </c>
       <c r="F28">
-        <v>6.483266147741473</v>
+        <v>4.39725147598435</v>
       </c>
       <c r="G28">
-        <v>-0.3514784600272166</v>
+        <v>-1.717244022253545</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.83930200226857</v>
       </c>
       <c r="E29">
-        <v>-32.28463898131352</v>
+        <v>-30.80433969836818</v>
       </c>
       <c r="F29">
-        <v>6.357559490703466</v>
+        <v>4.586277862933456</v>
       </c>
       <c r="G29">
-        <v>-1.004572952378018</v>
+        <v>-2.75983412893622</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-8.034202728549381</v>
       </c>
       <c r="E30">
-        <v>-30.42210252856574</v>
+        <v>-32.44241554421476</v>
       </c>
       <c r="F30">
-        <v>6.315694224828825</v>
+        <v>3.823099484518679</v>
       </c>
       <c r="G30">
-        <v>-0.2572470917974015</v>
+        <v>-3.38181942485449</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.221378321007027</v>
       </c>
       <c r="E31">
-        <v>-29.98089330599842</v>
+        <v>-31.98511665349819</v>
       </c>
       <c r="F31">
-        <v>6.178854115205279</v>
+        <v>4.149867109757215</v>
       </c>
       <c r="G31">
-        <v>-0.3586954493028278</v>
+        <v>-2.591711384269872</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-8.399505843228306</v>
       </c>
       <c r="E32">
-        <v>-30.38778575253562</v>
+        <v>-30.51127044601378</v>
       </c>
       <c r="F32">
-        <v>6.113660861196215</v>
+        <v>4.345104791306674</v>
       </c>
       <c r="G32">
-        <v>-1.544810947295066</v>
+        <v>-2.389979981288843</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-8.56442284904926</v>
       </c>
       <c r="E33">
-        <v>-30.53651895284354</v>
+        <v>-28.29304726657054</v>
       </c>
       <c r="F33">
-        <v>6.425283506765404</v>
+        <v>3.77272179934855</v>
       </c>
       <c r="G33">
-        <v>-0.4956957553544873</v>
+        <v>-3.140593213589956</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-8.715589998982036</v>
       </c>
       <c r="E34">
-        <v>-30.50464302430355</v>
+        <v>-28.24620020296119</v>
       </c>
       <c r="F34">
-        <v>6.883595329046257</v>
+        <v>4.203939580828064</v>
       </c>
       <c r="G34">
-        <v>-0.6561016183687941</v>
+        <v>-3.591032660754272</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-8.846928014002684</v>
       </c>
       <c r="E35">
-        <v>-30.00373719313011</v>
+        <v>-31.42999366726792</v>
       </c>
       <c r="F35">
-        <v>6.703455115988681</v>
+        <v>4.71305827258213</v>
       </c>
       <c r="G35">
-        <v>-0.6934180876874589</v>
+        <v>-2.776982754829644</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-8.957932615930918</v>
       </c>
       <c r="E36">
-        <v>-29.35157353738948</v>
+        <v>-30.94521146779879</v>
       </c>
       <c r="F36">
-        <v>6.323226330162655</v>
+        <v>4.812435818775955</v>
       </c>
       <c r="G36">
-        <v>-1.418526877154027</v>
+        <v>-3.186762081680632</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-9.03816907321211</v>
       </c>
       <c r="E37">
-        <v>-27.73043871280559</v>
+        <v>-27.94221279977429</v>
       </c>
       <c r="F37">
-        <v>6.700103994271611</v>
+        <v>3.933148041170735</v>
       </c>
       <c r="G37">
-        <v>-1.598269636663217</v>
+        <v>-2.393191210461936</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-9.08617305787946</v>
       </c>
       <c r="E38">
-        <v>-27.52754949183993</v>
+        <v>-29.66121700461195</v>
       </c>
       <c r="F38">
-        <v>6.531341124510552</v>
+        <v>4.492954824454356</v>
       </c>
       <c r="G38">
-        <v>-1.66702635696834</v>
+        <v>-2.587480507070683</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-9.096151466353859</v>
       </c>
       <c r="E39">
-        <v>-26.29767029304476</v>
+        <v>-27.85976740199064</v>
       </c>
       <c r="F39">
-        <v>6.825109069589078</v>
+        <v>4.381981383547682</v>
       </c>
       <c r="G39">
-        <v>-1.265761753244358</v>
+        <v>-3.291285935992041</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-9.069648004416628</v>
       </c>
       <c r="E40">
-        <v>-26.57618955841251</v>
+        <v>-26.4323018252928</v>
       </c>
       <c r="F40">
-        <v>6.414645754131397</v>
+        <v>5.279128612761313</v>
       </c>
       <c r="G40">
-        <v>-1.749677436901785</v>
+        <v>-2.352362252326104</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-9.004736340966689</v>
       </c>
       <c r="E41">
-        <v>-26.50910474446288</v>
+        <v>-26.92373182460518</v>
       </c>
       <c r="F41">
-        <v>6.987052501678254</v>
+        <v>4.539832519551363</v>
       </c>
       <c r="G41">
-        <v>-2.576701370794816</v>
+        <v>-5.385189436853371</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-8.903134790059063</v>
       </c>
       <c r="E42">
-        <v>-27.13478135573266</v>
+        <v>-23.55754501269152</v>
       </c>
       <c r="F42">
-        <v>6.863525023979892</v>
+        <v>4.451651774179695</v>
       </c>
       <c r="G42">
-        <v>-1.760297666991766</v>
+        <v>-3.415216208254658</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-8.768820165631427</v>
       </c>
       <c r="E43">
-        <v>-25.35963765862191</v>
+        <v>-24.2659976003475</v>
       </c>
       <c r="F43">
-        <v>7.501859865080577</v>
+        <v>5.294202325664466</v>
       </c>
       <c r="G43">
-        <v>-2.50918279452138</v>
+        <v>-2.2842477778556</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.606983045438882</v>
       </c>
       <c r="E44">
-        <v>-23.07480062652584</v>
+        <v>-23.51645363954592</v>
       </c>
       <c r="F44">
-        <v>7.030925906653673</v>
+        <v>4.175857307535492</v>
       </c>
       <c r="G44">
-        <v>-2.454621693488652</v>
+        <v>-4.439346713010357</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-8.427859714395273</v>
       </c>
       <c r="E45">
-        <v>-22.6041200951166</v>
+        <v>-23.32451879720481</v>
       </c>
       <c r="F45">
-        <v>7.721006754835427</v>
+        <v>4.395674104892572</v>
       </c>
       <c r="G45">
-        <v>-3.197319411405368</v>
+        <v>-4.053059017306038</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-8.235631361652713</v>
       </c>
       <c r="E46">
-        <v>-21.83983595142005</v>
+        <v>-20.94359660361399</v>
       </c>
       <c r="F46">
-        <v>7.523583559122661</v>
+        <v>4.502046880114893</v>
       </c>
       <c r="G46">
-        <v>-3.38963562287271</v>
+        <v>-4.718260174693954</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-8.039910700472078</v>
       </c>
       <c r="E47">
-        <v>-21.6206532809748</v>
+        <v>-23.11099671926915</v>
       </c>
       <c r="F47">
-        <v>7.359419771340038</v>
+        <v>4.503008189605565</v>
       </c>
       <c r="G47">
-        <v>-2.182474986887325</v>
+        <v>-5.098823937160874</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.844625028984072</v>
       </c>
       <c r="E48">
-        <v>-20.97243845456885</v>
+        <v>-19.70577446140936</v>
       </c>
       <c r="F48">
-        <v>7.582896513067698</v>
+        <v>5.209567497837466</v>
       </c>
       <c r="G48">
-        <v>-3.144228192592076</v>
+        <v>-4.679156010784083</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.661827106640178</v>
       </c>
       <c r="E49">
-        <v>-21.28691380355751</v>
+        <v>-21.51221897086113</v>
       </c>
       <c r="F49">
-        <v>7.220400482376848</v>
+        <v>4.826191888357462</v>
       </c>
       <c r="G49">
-        <v>-3.27703072689994</v>
+        <v>-2.312208645480284</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.49268001065714</v>
       </c>
       <c r="E50">
-        <v>-18.94757658677912</v>
+        <v>-20.6791654208841</v>
       </c>
       <c r="F50">
-        <v>7.286415679756026</v>
+        <v>4.904252752929472</v>
       </c>
       <c r="G50">
-        <v>-3.623055567755642</v>
+        <v>-5.249553075563891</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.342691582661281</v>
       </c>
       <c r="E51">
-        <v>-19.33009225773303</v>
+        <v>-21.01046857928526</v>
       </c>
       <c r="F51">
-        <v>7.152749316787022</v>
+        <v>4.958741738656082</v>
       </c>
       <c r="G51">
-        <v>-3.70851067976085</v>
+        <v>-5.00199710122827</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.212049899750351</v>
       </c>
       <c r="E52">
-        <v>-19.70397665722832</v>
+        <v>-18.034174322484</v>
       </c>
       <c r="F52">
-        <v>7.215383302036736</v>
+        <v>4.87964671412129</v>
       </c>
       <c r="G52">
-        <v>-3.137107209137104</v>
+        <v>-4.97288085321038</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.103575136849549</v>
       </c>
       <c r="E53">
-        <v>-18.68206309876139</v>
+        <v>-18.04276030920254</v>
       </c>
       <c r="F53">
-        <v>7.417244041724564</v>
+        <v>4.912044586033435</v>
       </c>
       <c r="G53">
-        <v>-3.588480230143494</v>
+        <v>-2.299959626984981</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.016888503259434</v>
       </c>
       <c r="E54">
-        <v>-18.83283864084678</v>
+        <v>-17.52505610369765</v>
       </c>
       <c r="F54">
-        <v>7.477694096516887</v>
+        <v>4.736763182724427</v>
       </c>
       <c r="G54">
-        <v>-3.26349390618986</v>
+        <v>-3.796836034748605</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.948019540855928</v>
       </c>
       <c r="E55">
-        <v>-16.85471062481621</v>
+        <v>-17.70977255847052</v>
       </c>
       <c r="F55">
-        <v>7.211397114247575</v>
+        <v>4.428832155644128</v>
       </c>
       <c r="G55">
-        <v>-4.243087641805743</v>
+        <v>-4.380905652605603</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.895214503498902</v>
       </c>
       <c r="E56">
-        <v>-14.92816192773301</v>
+        <v>-15.64808514005042</v>
       </c>
       <c r="F56">
-        <v>7.566343618839526</v>
+        <v>5.159943656683087</v>
       </c>
       <c r="G56">
-        <v>-3.920918592106028</v>
+        <v>-3.772500214489422</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.853638729418921</v>
       </c>
       <c r="E57">
-        <v>-17.26837766846888</v>
+        <v>-14.31404651060482</v>
       </c>
       <c r="F57">
-        <v>7.383748661613019</v>
+        <v>5.039504405519832</v>
       </c>
       <c r="G57">
-        <v>-4.190800885558494</v>
+        <v>-4.710288381035389</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.825180739502267</v>
       </c>
       <c r="E58">
-        <v>-15.58362231255123</v>
+        <v>-17.52333981204874</v>
       </c>
       <c r="F58">
-        <v>7.460369937507895</v>
+        <v>4.931034803665469</v>
       </c>
       <c r="G58">
-        <v>-4.639730723956903</v>
+        <v>-3.656568220249685</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.802533292445018</v>
       </c>
       <c r="E59">
-        <v>-15.36905868559381</v>
+        <v>-15.83285140803738</v>
       </c>
       <c r="F59">
-        <v>7.480503590810876</v>
+        <v>4.460602880013758</v>
       </c>
       <c r="G59">
-        <v>-5.163502065361615</v>
+        <v>-4.613266222915969</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.78508974769808</v>
       </c>
       <c r="E60">
-        <v>-14.61847317577046</v>
+        <v>-14.4747982809291</v>
       </c>
       <c r="F60">
-        <v>7.481672365776471</v>
+        <v>4.990409522141209</v>
       </c>
       <c r="G60">
-        <v>-3.938037423089599</v>
+        <v>-4.240386236645698</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.768693100386356</v>
       </c>
       <c r="E61">
-        <v>-15.80991468718853</v>
+        <v>-14.32890896229799</v>
       </c>
       <c r="F61">
-        <v>7.380331024247501</v>
+        <v>4.456995197938387</v>
       </c>
       <c r="G61">
-        <v>-4.276302345201251</v>
+        <v>-6.090050929801756</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.755195083291015</v>
       </c>
       <c r="E62">
-        <v>-15.30624422263341</v>
+        <v>-13.73393993327423</v>
       </c>
       <c r="F62">
-        <v>7.376311578634115</v>
+        <v>4.75246562687601</v>
       </c>
       <c r="G62">
-        <v>-4.618506816504635</v>
+        <v>-4.471230577099078</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.741182357448966</v>
       </c>
       <c r="E63">
-        <v>-14.55412808859547</v>
+        <v>-14.7791389050886</v>
       </c>
       <c r="F63">
-        <v>7.396494326820476</v>
+        <v>4.677640273489242</v>
       </c>
       <c r="G63">
-        <v>-4.917641090342101</v>
+        <v>-5.125890957489955</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.726012633220783</v>
       </c>
       <c r="E64">
-        <v>-12.17102769900696</v>
+        <v>-12.18812721685992</v>
       </c>
       <c r="F64">
-        <v>7.51381526103623</v>
+        <v>4.340082859848817</v>
       </c>
       <c r="G64">
-        <v>-4.437463012598512</v>
+        <v>-5.857630769671683</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.709228648460551</v>
       </c>
       <c r="E65">
-        <v>-12.06296925223593</v>
+        <v>-13.37878530227467</v>
       </c>
       <c r="F65">
-        <v>7.030471383055942</v>
+        <v>5.414719178417577</v>
       </c>
       <c r="G65">
-        <v>-4.35707303526839</v>
+        <v>-4.343953343296258</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.690794709240628</v>
       </c>
       <c r="E66">
-        <v>-13.39056386316862</v>
+        <v>-14.40021884249678</v>
       </c>
       <c r="F66">
-        <v>6.924074852244889</v>
+        <v>4.596508603147194</v>
       </c>
       <c r="G66">
-        <v>-4.805459944198358</v>
+        <v>-4.539341741024043</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.672265034814619</v>
       </c>
       <c r="E67">
-        <v>-12.57277127059744</v>
+        <v>-12.56132781678005</v>
       </c>
       <c r="F67">
-        <v>7.242372818247655</v>
+        <v>4.170081532061884</v>
       </c>
       <c r="G67">
-        <v>-4.536663509682772</v>
+        <v>-5.644590543128504</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-6.650332178282765</v>
       </c>
       <c r="E68">
-        <v>-11.4787644059284</v>
+        <v>-11.12940169318465</v>
       </c>
       <c r="F68">
-        <v>6.518544780713802</v>
+        <v>3.49919044845751</v>
       </c>
       <c r="G68">
-        <v>-4.013567519568071</v>
+        <v>-4.711122638511286</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.625835102166259</v>
       </c>
       <c r="E69">
-        <v>-12.50987982357891</v>
+        <v>-12.92350158249151</v>
       </c>
       <c r="F69">
-        <v>7.178202638259965</v>
+        <v>3.982716452618074</v>
       </c>
       <c r="G69">
-        <v>-4.915336950646768</v>
+        <v>-5.594356325115603</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.59534985424155</v>
       </c>
       <c r="E70">
-        <v>-12.68296262862608</v>
+        <v>-12.47095758948298</v>
       </c>
       <c r="F70">
-        <v>6.438947721403816</v>
+        <v>3.68960099437671</v>
       </c>
       <c r="G70">
-        <v>-3.78373289550417</v>
+        <v>-4.942735025529776</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-6.562200335637342</v>
       </c>
       <c r="E71">
-        <v>-11.69964072565252</v>
+        <v>-11.95034610366517</v>
       </c>
       <c r="F71">
-        <v>5.783602295065394</v>
+        <v>3.703269960132868</v>
       </c>
       <c r="G71">
-        <v>-4.068568923157523</v>
+        <v>-5.521454801795312</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.521200460530613</v>
       </c>
       <c r="E72">
-        <v>-11.46653752610769</v>
+        <v>-10.52888528350149</v>
       </c>
       <c r="F72">
-        <v>6.144970727144453</v>
+        <v>3.884583699273784</v>
       </c>
       <c r="G72">
-        <v>-5.43547993414044</v>
+        <v>-7.577032116948499</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.47295345870225</v>
       </c>
       <c r="E73">
-        <v>-13.03107095406971</v>
+        <v>-12.27511467407326</v>
       </c>
       <c r="F73">
-        <v>6.477536299739413</v>
+        <v>3.639313580443762</v>
       </c>
       <c r="G73">
-        <v>-4.435364126726614</v>
+        <v>-6.179227094993104</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-6.415403745351661</v>
       </c>
       <c r="E74">
-        <v>-11.95363377579474</v>
+        <v>-12.2659264003117</v>
       </c>
       <c r="F74">
-        <v>6.463187924145531</v>
+        <v>3.697188529417581</v>
       </c>
       <c r="G74">
-        <v>-4.791251082743806</v>
+        <v>-5.019254975124491</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.350191259608189</v>
       </c>
       <c r="E75">
-        <v>-10.64581501085355</v>
+        <v>-13.2368131136602</v>
       </c>
       <c r="F75">
-        <v>5.919264127487853</v>
+        <v>3.76724534429296</v>
       </c>
       <c r="G75">
-        <v>-4.243289585083638</v>
+        <v>-3.331886466485663</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.277616360093953</v>
       </c>
       <c r="E76">
-        <v>-11.19236106731329</v>
+        <v>-12.09105031955749</v>
       </c>
       <c r="F76">
-        <v>6.160541723705053</v>
+        <v>3.832090183000628</v>
       </c>
       <c r="G76">
-        <v>-3.587695630850687</v>
+        <v>-5.761631570123897</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.196799172605706</v>
       </c>
       <c r="E77">
-        <v>-12.89358648319684</v>
+        <v>-13.26740748405602</v>
       </c>
       <c r="F77">
-        <v>5.731522126036169</v>
+        <v>4.043950441838541</v>
       </c>
       <c r="G77">
-        <v>-4.283555750477794</v>
+        <v>-4.281092704596577</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-6.10926355194261</v>
       </c>
       <c r="E78">
-        <v>-13.26333185744911</v>
+        <v>-14.08152295573297</v>
       </c>
       <c r="F78">
-        <v>5.972170991004939</v>
+        <v>3.363219793381541</v>
       </c>
       <c r="G78">
-        <v>-3.562323609837712</v>
+        <v>-3.928830795944886</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.015274879089501</v>
       </c>
       <c r="E79">
-        <v>-12.32174889940425</v>
+        <v>-14.44970147797859</v>
       </c>
       <c r="F79">
-        <v>5.568633221515475</v>
+        <v>3.775556632937187</v>
       </c>
       <c r="G79">
-        <v>-3.706527662982826</v>
+        <v>-3.210359650284557</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.92029298805571</v>
       </c>
       <c r="E80">
-        <v>-13.59166433690124</v>
+        <v>-14.41356425539738</v>
       </c>
       <c r="F80">
-        <v>6.194832124186148</v>
+        <v>3.002353396077678</v>
       </c>
       <c r="G80">
-        <v>-3.870939286099651</v>
+        <v>-5.21139903822379</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-5.823536182053845</v>
       </c>
       <c r="E81">
-        <v>-15.34784278486787</v>
+        <v>-14.62521154509387</v>
       </c>
       <c r="F81">
-        <v>5.087487527345816</v>
+        <v>2.980347802382647</v>
       </c>
       <c r="G81">
-        <v>-2.431461116895911</v>
+        <v>-4.928800939354984</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-5.730227080535337</v>
       </c>
       <c r="E82">
-        <v>-14.52291784573461</v>
+        <v>-15.23799559086381</v>
       </c>
       <c r="F82">
-        <v>5.718771709710966</v>
+        <v>3.082300454394976</v>
       </c>
       <c r="G82">
-        <v>-3.319968502544287</v>
+        <v>-3.13267107811448</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-5.642513668169093</v>
       </c>
       <c r="E83">
-        <v>-14.70733994969698</v>
+        <v>-14.76465231673806</v>
       </c>
       <c r="F83">
-        <v>5.492908323168738</v>
+        <v>3.170376675176226</v>
       </c>
       <c r="G83">
-        <v>-2.91132138226773</v>
+        <v>-3.456154414393286</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-5.568748186018268</v>
       </c>
       <c r="E84">
-        <v>-17.08031014293033</v>
+        <v>-17.24701232810069</v>
       </c>
       <c r="F84">
-        <v>5.361034715296011</v>
+        <v>3.161460410872302</v>
       </c>
       <c r="G84">
-        <v>-2.490084257305325</v>
+        <v>-3.13126409626029</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.511655032270412</v>
       </c>
       <c r="E85">
-        <v>-16.75343583210867</v>
+        <v>-15.9718982024429</v>
       </c>
       <c r="F85">
-        <v>5.228077852577123</v>
+        <v>3.419747008621321</v>
       </c>
       <c r="G85">
-        <v>-2.002133018635527</v>
+        <v>-5.374148767479901</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.476320744190818</v>
       </c>
       <c r="E86">
-        <v>-18.15981683382681</v>
+        <v>-20.22394509973704</v>
       </c>
       <c r="F86">
-        <v>5.278943319169207</v>
+        <v>3.118131800731794</v>
       </c>
       <c r="G86">
-        <v>-1.037595644132249</v>
+        <v>-3.128897056199711</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.466980343887058</v>
       </c>
       <c r="E87">
-        <v>-18.27126257915558</v>
+        <v>-21.78494631797308</v>
       </c>
       <c r="F87">
-        <v>5.360570689462786</v>
+        <v>3.207807564487637</v>
       </c>
       <c r="G87">
-        <v>-1.866039802061628</v>
+        <v>-4.37555912155968</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-5.487978882798913</v>
       </c>
       <c r="E88">
-        <v>-20.5571321033254</v>
+        <v>-21.44940450790073</v>
       </c>
       <c r="F88">
-        <v>5.354756905047209</v>
+        <v>2.19749346167445</v>
       </c>
       <c r="G88">
-        <v>-1.349753604121207</v>
+        <v>-1.969404965434292</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-5.542868967142019</v>
       </c>
       <c r="E89">
-        <v>-21.54516361926693</v>
+        <v>-23.62217086525498</v>
       </c>
       <c r="F89">
-        <v>4.491000531354703</v>
+        <v>2.454877347051669</v>
       </c>
       <c r="G89">
-        <v>-1.137527771780689</v>
+        <v>-1.559387279304477</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.629920953344346</v>
       </c>
       <c r="E90">
-        <v>-22.36555102744451</v>
+        <v>-23.6612063112011</v>
       </c>
       <c r="F90">
-        <v>4.291710146367634</v>
+        <v>2.501463640260236</v>
       </c>
       <c r="G90">
-        <v>-1.146429828735789</v>
+        <v>-2.980203903303345</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.750594882843641</v>
       </c>
       <c r="E91">
-        <v>-22.6702448725766</v>
+        <v>-24.44451004572986</v>
       </c>
       <c r="F91">
-        <v>4.677519911839669</v>
+        <v>2.390665990710176</v>
       </c>
       <c r="G91">
-        <v>-0.7885863403048877</v>
+        <v>-3.645113732683806</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.90072017672666</v>
       </c>
       <c r="E92">
-        <v>-24.00515296903168</v>
+        <v>-26.64213772538622</v>
       </c>
       <c r="F92">
-        <v>4.615589092016409</v>
+        <v>1.49142668598225</v>
       </c>
       <c r="G92">
-        <v>0.2861756479284246</v>
+        <v>-1.91217887524245</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.080528084571573</v>
       </c>
       <c r="E93">
-        <v>-27.50401501242207</v>
+        <v>-28.03121542792104</v>
       </c>
       <c r="F93">
-        <v>3.850106421494667</v>
+        <v>1.486788011355928</v>
       </c>
       <c r="G93">
-        <v>-1.204470313130291</v>
+        <v>-1.765879246770978</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.278817381319436</v>
       </c>
       <c r="E94">
-        <v>-28.89582791325753</v>
+        <v>-31.21724369415056</v>
       </c>
       <c r="F94">
-        <v>3.404681214247746</v>
+        <v>1.762053520224374</v>
       </c>
       <c r="G94">
-        <v>-0.4329741595674554</v>
+        <v>-2.955113278661209</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.492077312518291</v>
       </c>
       <c r="E95">
-        <v>-29.36448874525935</v>
+        <v>-30.75043953649189</v>
       </c>
       <c r="F95">
-        <v>3.055634014190807</v>
+        <v>1.227289878581597</v>
       </c>
       <c r="G95">
-        <v>-1.185884910472823</v>
+        <v>-2.09192163475164</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-6.714409783579898</v>
       </c>
       <c r="E96">
-        <v>-33.45756582675123</v>
+        <v>-36.08987040521885</v>
       </c>
       <c r="F96">
-        <v>2.928053833054836</v>
+        <v>0.7123225608818139</v>
       </c>
       <c r="G96">
-        <v>-0.4201093796018476</v>
+        <v>-2.954159841545899</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-6.940566196897865</v>
       </c>
       <c r="E97">
-        <v>-34.73849224879788</v>
+        <v>-35.46274241802961</v>
       </c>
       <c r="F97">
-        <v>2.53472621560221</v>
+        <v>0.7698031670826886</v>
       </c>
       <c r="G97">
-        <v>-0.257594699079025</v>
+        <v>-2.919620919934683</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-7.168693250821123</v>
       </c>
       <c r="E98">
-        <v>-36.32650128601565</v>
+        <v>-39.29970033083268</v>
       </c>
       <c r="F98">
-        <v>2.404569344941819</v>
+        <v>0.744999165035076</v>
       </c>
       <c r="G98">
-        <v>-0.7932641411518779</v>
+        <v>-2.696990042964235</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.388425083265628</v>
       </c>
       <c r="E99">
-        <v>-38.73515359019244</v>
+        <v>-40.82004038095383</v>
       </c>
       <c r="F99">
-        <v>1.866981955651814</v>
+        <v>0.03449563722077267</v>
       </c>
       <c r="G99">
-        <v>-1.1105865521821</v>
+        <v>-3.901773707252423</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.608169330184387</v>
       </c>
       <c r="E100">
-        <v>-41.1557112525354</v>
+        <v>-42.31682104505009</v>
       </c>
       <c r="F100">
-        <v>1.509792923483601</v>
+        <v>-0.2913946149406105</v>
       </c>
       <c r="G100">
-        <v>-0.2015902001911743</v>
+        <v>-3.933654260795604</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.810339244755434</v>
       </c>
       <c r="E101">
-        <v>-43.19813907100087</v>
+        <v>-43.33788325040357</v>
       </c>
       <c r="F101">
-        <v>1.235650262109202</v>
+        <v>-0.9871926414771008</v>
       </c>
       <c r="G101">
-        <v>-0.3790950309158168</v>
+        <v>-3.262573574529942</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.021979279278661</v>
       </c>
       <c r="E102">
-        <v>-44.81037544415969</v>
+        <v>-44.02856610605346</v>
       </c>
       <c r="F102">
-        <v>1.482847751038314</v>
+        <v>-0.7791982087787764</v>
       </c>
       <c r="G102">
-        <v>-1.029031262822154</v>
+        <v>-4.265480171833373</v>
       </c>
     </row>
   </sheetData>
